--- a/data/datos_fondos.xlsx
+++ b/data/datos_fondos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6545ea455a795f0/Documentos/factsheets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_F2C1C925891D1C937C5806DC84D384AFB2134F96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D5EA3CA-5E00-48C8-A419-DCD52DBF8B0B}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="11_F2C1C925891D1C937C5806DC84D384AFB2134F96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8320958D-0F15-4154-B495-92A8D0A9724A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS_FONDO" sheetId="1" r:id="rId1"/>
@@ -1212,7 +1212,7 @@
       <c r="A4" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>85</v>
       </c>
       <c r="C4" s="9">
@@ -1246,7 +1246,7 @@
       <c r="A6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="9">
@@ -1280,7 +1280,7 @@
       <c r="A8" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>83</v>
       </c>
       <c r="C8" s="9">
@@ -1447,7 +1447,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1481,7 +1481,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>101</v>
       </c>
       <c r="B7" s="4" t="s">

--- a/data/datos_fondos.xlsx
+++ b/data/datos_fondos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d6545ea455a795f0/Documentos/factsheets/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="11_F2C1C925891D1C937C5806DC84D384AFB2134F96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8320958D-0F15-4154-B495-92A8D0A9724A}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="11_F2C1C925891D1C937C5806DC84D384AFB2134F96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69C11A45-DCAB-486C-804B-04AD9FBA6399}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATOS_FONDO" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="101">
   <si>
     <t>DATOS_FONDO — una fila por fondo</t>
   </si>
@@ -186,9 +186,6 @@
     <t>otros</t>
   </si>
   <si>
-    <t>SOCIEDAD GERENTE S.A.</t>
-  </si>
-  <si>
     <t>BANCO DEPOSITARIO S.A.</t>
   </si>
   <si>
@@ -225,15 +222,9 @@
     <t>https://gerente.com.ar/impositivo</t>
   </si>
   <si>
-    <t>fondo_dos</t>
-  </si>
-  <si>
     <t>money_market</t>
   </si>
   <si>
-    <t>FONDO DOS - MONEY MARKET</t>
-  </si>
-  <si>
     <t>Fondo Común de Dinero Clásico</t>
   </si>
   <si>
@@ -250,9 +241,6 @@
   </si>
   <si>
     <t>01/03/2015</t>
-  </si>
-  <si>
-    <t>A</t>
   </si>
   <si>
     <t>El FCI invierte en instrumentos de alta liquidez denominados en pesos.</t>
@@ -299,24 +287,9 @@
     <t>7 dias</t>
   </si>
   <si>
-    <t>68.10%</t>
-  </si>
-  <si>
-    <t>69.30%</t>
-  </si>
-  <si>
-    <t>71.20%</t>
-  </si>
-  <si>
-    <t>74.50%</t>
-  </si>
-  <si>
     <t>HONORARIOS — una fila por fondo y concepto</t>
   </si>
   <si>
-    <t>Ingresar porcentaje anual para cada clase. Dejar vacío si la clase no existe para ese fondo.</t>
-  </si>
-  <si>
     <t>concepto</t>
   </si>
   <si>
@@ -326,19 +299,10 @@
     <t>Comisiones suscripción, rescate y transferencia</t>
   </si>
   <si>
-    <t>0.00%</t>
-  </si>
-  <si>
     <t>Honorarios de éxito</t>
   </si>
   <si>
     <t>Gastos ordinarios de gestión (Prom. últ. 3 meses)</t>
-  </si>
-  <si>
-    <t>1.50%</t>
-  </si>
-  <si>
-    <t>0.10%</t>
   </si>
   <si>
     <t>(*) Los Honorarios de la Sociedad Depositaria incluyen IVA.
@@ -368,6 +332,18 @@
   </si>
   <si>
     <t>FCI de Renta Fija</t>
+  </si>
+  <si>
+    <t>gainvest_pesos</t>
+  </si>
+  <si>
+    <t>Gainvest Pesos</t>
+  </si>
+  <si>
+    <t>Contado Inmediato</t>
+  </si>
+  <si>
+    <t>AAA (arg)</t>
   </si>
 </sst>
 </file>
@@ -417,7 +393,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,6 +408,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -462,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -492,12 +474,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -821,58 +812,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
     </row>
     <row r="2" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12"/>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
+      <c r="R2" s="15"/>
+      <c r="S2" s="15"/>
+      <c r="T2" s="15"/>
+      <c r="U2" s="15"/>
+      <c r="V2" s="15"/>
+      <c r="W2" s="15"/>
     </row>
     <row r="3" spans="1:23" ht="24" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1018,138 +1009,140 @@
     </row>
     <row r="5" spans="1:23" ht="48" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="F5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="N5" s="7">
         <v>42278</v>
       </c>
       <c r="O5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="Q5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="S5" s="4" t="s">
+      <c r="T5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="U5" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="V5" s="4"/>
       <c r="W5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="24" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I6" s="6" t="s">
+      <c r="L6" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="O6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q6" s="6"/>
+      <c r="Q6" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="R6" s="6"/>
       <c r="S6" s="6" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1163,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -1172,48 +1165,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="A1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
       <c r="F1" s="8"/>
       <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
+      <c r="A2" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C4" s="9">
         <v>5</v>
@@ -1227,10 +1220,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C5" s="10">
         <v>10</v>
@@ -1244,10 +1237,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C6" s="9">
         <v>15</v>
@@ -1261,10 +1254,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C7" s="10">
         <v>50</v>
@@ -1278,10 +1271,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C8" s="9">
         <v>30</v>
@@ -1295,10 +1288,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C9" s="10">
         <v>48</v>
@@ -1312,68 +1305,105 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+        <v>81</v>
+      </c>
+      <c r="C10" s="9">
+        <v>25</v>
+      </c>
+      <c r="D10" s="9">
+        <v>25</v>
+      </c>
+      <c r="E10" s="9">
+        <v>26</v>
+      </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
+        <v>76</v>
+      </c>
+      <c r="C11" s="10">
+        <v>25</v>
+      </c>
+      <c r="D11" s="10">
+        <v>25</v>
+      </c>
+      <c r="E11" s="10">
+        <v>26</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="C12" s="9">
+        <v>25</v>
+      </c>
+      <c r="D12" s="9">
+        <v>25</v>
+      </c>
+      <c r="E12" s="9">
+        <v>26</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
+        <v>78</v>
+      </c>
+      <c r="C13" s="10">
+        <v>25</v>
+      </c>
+      <c r="D13" s="10">
+        <v>25</v>
+      </c>
+      <c r="E13" s="10">
+        <v>26</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+        <v>79</v>
+      </c>
+      <c r="C14" s="9">
+        <v>25</v>
+      </c>
+      <c r="D14" s="9">
+        <v>25</v>
+      </c>
+      <c r="E14" s="9">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="10">
+        <v>25</v>
+      </c>
+      <c r="D15" s="10">
+        <v>25</v>
+      </c>
+      <c r="E15" s="10">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1386,183 +1416,189 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
     <col min="3" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="9">
+      <c r="B2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" s="9">
         <v>2.5</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D3" s="9">
         <v>2</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E3" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="10">
+    <row r="4" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="13">
         <v>0</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D4" s="13">
         <v>0</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E4" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="9">
+    <row r="5" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="9">
         <v>0</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D5" s="9">
         <v>0</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E5" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="6" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="D6" s="13">
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="13">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="E7" s="10">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="B7" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="E7" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
+      <c r="B8" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="13">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" s="15"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
+  <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
